--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52487-2024 artfynd.xlsx
+++ b/artfynd/A 52487-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>136128123</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>136128462</v>
       </c>
       <c r="B95" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
